--- a/codespace/results/ch3_fw3_concordant_lda_random_split_cv_confusion_matrix.xlsx
+++ b/codespace/results/ch3_fw3_concordant_lda_random_split_cv_confusion_matrix.xlsx
@@ -453,12 +453,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>32.77 +/- 0.02</t>
+          <t>33.78 +/- 0.01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.23 +/- 0.02</t>
+          <t>0.21 +/- 0.01</t>
         </is>
       </c>
     </row>
@@ -470,12 +470,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.44 +/- 0.02</t>
+          <t>2.13 +/- 0.03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.56 +/- 0.02</t>
+          <t>6.87 +/- 0.03</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>96% +/- 0% (n = 44)</t>
+          <t>95% +/- 0% (n = 43)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>

--- a/codespace/results/ch3_fw3_concordant_lda_random_split_cv_confusion_matrix.xlsx
+++ b/codespace/results/ch3_fw3_concordant_lda_random_split_cv_confusion_matrix.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
